--- a/backtest_runs/20260410_193731/by_symbol/ISIL/ISIL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/ISIL/ISIL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -584,10 +584,10 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>103181.36</v>
@@ -633,7 +633,7 @@
         <v>-63.44000000000142</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>103117.92</v>
@@ -679,7 +679,7 @@
         <v>-1022.840000000004</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>102095.08</v>
@@ -909,7 +909,7 @@
         <v>-2876.640000000009</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>99218.43999999999</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>99218.43999999999</v>
@@ -1277,7 +1277,7 @@
         <v>-321.3599999999915</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>98897.08</v>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>98897.08</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>98897.08</v>
@@ -1507,7 +1507,7 @@
         <v>-2031.120000000009</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>96865.95999999999</v>
